--- a/data/base/Backlog_45.xlsx
+++ b/data/base/Backlog_45.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70BEAE08-6699-4D9F-8EEF-A6ECA4BF5B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26F0308B-35E4-4EED-830B-D686A9BE3584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="32">
   <si>
     <t>Setor</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>Luana Giese</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -670,7 +673,7 @@
         <v>45971</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>13</v>
@@ -705,7 +708,7 @@
         <v>45971</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>13</v>
@@ -845,7 +848,7 @@
         <v>45971</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>13</v>
@@ -880,7 +883,7 @@
         <v>45971</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>13</v>
@@ -950,7 +953,7 @@
         <v>45971</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>13</v>
@@ -985,7 +988,7 @@
         <v>45971</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>13</v>
@@ -1020,7 +1023,7 @@
         <v>45971</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>13</v>
@@ -1055,7 +1058,7 @@
         <v>45971</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>13</v>
@@ -1090,7 +1093,7 @@
         <v>45971</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>13</v>
@@ -1160,7 +1163,7 @@
         <v>45971</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>13</v>
@@ -1265,7 +1268,7 @@
         <v>45971</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>13</v>
@@ -1335,7 +1338,7 @@
         <v>45971</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>13</v>
@@ -1370,7 +1373,7 @@
         <v>45971</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>13</v>
@@ -1405,7 +1408,7 @@
         <v>45971</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>13</v>
@@ -1440,7 +1443,7 @@
         <v>45971</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>13</v>
@@ -1475,7 +1478,7 @@
         <v>45971</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>13</v>
@@ -1510,7 +1513,7 @@
         <v>45971</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>13</v>
@@ -1545,7 +1548,7 @@
         <v>45971</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>13</v>
@@ -1580,7 +1583,7 @@
         <v>45971</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>13</v>
@@ -1685,7 +1688,7 @@
         <v>45971</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>13</v>
@@ -1755,7 +1758,7 @@
         <v>45971</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>13</v>
@@ -1790,7 +1793,7 @@
         <v>45971</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>13</v>
@@ -1825,7 +1828,7 @@
         <v>45971</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>13</v>
@@ -1860,7 +1863,7 @@
         <v>45971</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>13</v>
@@ -1895,7 +1898,7 @@
         <v>45971</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>13</v>
@@ -1930,7 +1933,7 @@
         <v>45971</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>13</v>
@@ -2000,7 +2003,7 @@
         <v>45971</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>13</v>
@@ -2275,7 +2278,7 @@
         <v>45971</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
@@ -2310,7 +2313,7 @@
         <v>45971</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>17</v>
@@ -2345,7 +2348,7 @@
         <v>45971</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>17</v>
@@ -2380,7 +2383,7 @@
         <v>45971</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>17</v>
@@ -2415,7 +2418,7 @@
         <v>45971</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>17</v>
@@ -2450,7 +2453,7 @@
         <v>45971</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>17</v>
@@ -2520,7 +2523,7 @@
         <v>45971</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>17</v>

--- a/data/base/Backlog_45.xlsx
+++ b/data/base/Backlog_45.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26F0308B-35E4-4EED-830B-D686A9BE3584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A262B06-A84C-41BE-BCC5-CA5D070D6BEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
@@ -100,9 +100,6 @@
     <t>Lourival Silva</t>
   </si>
   <si>
-    <t>Erick Silva</t>
-  </si>
-  <si>
     <t>Felipe Nascimento</t>
   </si>
   <si>
@@ -137,6 +134,9 @@
   </si>
   <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Erick da Silva</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -664,16 +664,16 @@
         <v>45975</v>
       </c>
       <c r="G2" s="9">
-        <v>5274</v>
+        <v>4677</v>
       </c>
       <c r="H2" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I2" s="2">
         <v>45971</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>13</v>
@@ -684,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
@@ -699,16 +699,16 @@
         <v>45975</v>
       </c>
       <c r="G3" s="9">
-        <v>5273</v>
+        <v>4134</v>
       </c>
       <c r="H3" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I3" s="2">
         <v>45971</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>13</v>
@@ -719,7 +719,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
@@ -734,10 +734,10 @@
         <v>45975</v>
       </c>
       <c r="G4" s="9">
-        <v>5205</v>
+        <v>3264</v>
       </c>
       <c r="H4" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I4" s="2">
         <v>45971</v>
@@ -754,7 +754,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -789,7 +789,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
@@ -824,7 +824,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
@@ -839,7 +839,7 @@
         <v>45975</v>
       </c>
       <c r="G7" s="9">
-        <v>5188</v>
+        <v>5186</v>
       </c>
       <c r="H7" s="3">
         <v>45962</v>
@@ -848,7 +848,7 @@
         <v>45971</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>13</v>
@@ -859,7 +859,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
@@ -874,7 +874,7 @@
         <v>45975</v>
       </c>
       <c r="G8" s="9">
-        <v>5186</v>
+        <v>5135</v>
       </c>
       <c r="H8" s="3">
         <v>45962</v>
@@ -883,7 +883,7 @@
         <v>45971</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>13</v>
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C9" s="9">
         <v>2025</v>
@@ -909,7 +909,7 @@
         <v>45975</v>
       </c>
       <c r="G9" s="9">
-        <v>5185</v>
+        <v>5130</v>
       </c>
       <c r="H9" s="3">
         <v>45962</v>
@@ -918,7 +918,7 @@
         <v>45971</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>13</v>
@@ -929,7 +929,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C10" s="9">
         <v>2025</v>
@@ -944,7 +944,7 @@
         <v>45975</v>
       </c>
       <c r="G10" s="9">
-        <v>5164</v>
+        <v>5127</v>
       </c>
       <c r="H10" s="3">
         <v>45962</v>
@@ -953,7 +953,7 @@
         <v>45971</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>13</v>
@@ -964,7 +964,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
@@ -979,7 +979,7 @@
         <v>45975</v>
       </c>
       <c r="G11" s="9">
-        <v>5135</v>
+        <v>5092</v>
       </c>
       <c r="H11" s="3">
         <v>45962</v>
@@ -988,7 +988,7 @@
         <v>45971</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>13</v>
@@ -999,7 +999,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
@@ -1014,7 +1014,7 @@
         <v>45975</v>
       </c>
       <c r="G12" s="9">
-        <v>5130</v>
+        <v>5055</v>
       </c>
       <c r="H12" s="3">
         <v>45962</v>
@@ -1023,7 +1023,7 @@
         <v>45971</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>13</v>
@@ -1034,7 +1034,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1049,7 +1049,7 @@
         <v>45975</v>
       </c>
       <c r="G13" s="9">
-        <v>5127</v>
+        <v>5016</v>
       </c>
       <c r="H13" s="3">
         <v>45962</v>
@@ -1058,7 +1058,7 @@
         <v>45971</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>13</v>
@@ -1069,7 +1069,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
@@ -1084,7 +1084,7 @@
         <v>45975</v>
       </c>
       <c r="G14" s="9">
-        <v>5092</v>
+        <v>4968</v>
       </c>
       <c r="H14" s="3">
         <v>45962</v>
@@ -1093,7 +1093,7 @@
         <v>45971</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>13</v>
@@ -1104,7 +1104,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1119,7 +1119,7 @@
         <v>45975</v>
       </c>
       <c r="G15" s="9">
-        <v>5055</v>
+        <v>4966</v>
       </c>
       <c r="H15" s="3">
         <v>45962</v>
@@ -1128,7 +1128,7 @@
         <v>45971</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>13</v>
@@ -1139,7 +1139,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
@@ -1154,7 +1154,7 @@
         <v>45975</v>
       </c>
       <c r="G16" s="9">
-        <v>5026</v>
+        <v>4944</v>
       </c>
       <c r="H16" s="3">
         <v>45962</v>
@@ -1163,7 +1163,7 @@
         <v>45971</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>13</v>
@@ -1174,7 +1174,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C17" s="9">
         <v>2025</v>
@@ -1189,7 +1189,7 @@
         <v>45975</v>
       </c>
       <c r="G17" s="9">
-        <v>5016</v>
+        <v>4905</v>
       </c>
       <c r="H17" s="3">
         <v>45962</v>
@@ -1198,7 +1198,7 @@
         <v>45971</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>13</v>
@@ -1209,7 +1209,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C18" s="9">
         <v>2025</v>
@@ -1224,7 +1224,7 @@
         <v>45975</v>
       </c>
       <c r="G18" s="9">
-        <v>4968</v>
+        <v>4896</v>
       </c>
       <c r="H18" s="3">
         <v>45962</v>
@@ -1233,7 +1233,7 @@
         <v>45971</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>13</v>
@@ -1244,7 +1244,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
@@ -1259,7 +1259,7 @@
         <v>45975</v>
       </c>
       <c r="G19" s="9">
-        <v>4966</v>
+        <v>4863</v>
       </c>
       <c r="H19" s="3">
         <v>45962</v>
@@ -1268,7 +1268,7 @@
         <v>45971</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>13</v>
@@ -1279,7 +1279,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C20" s="9">
         <v>2025</v>
@@ -1294,7 +1294,7 @@
         <v>45975</v>
       </c>
       <c r="G20" s="9">
-        <v>4944</v>
+        <v>4837</v>
       </c>
       <c r="H20" s="3">
         <v>45962</v>
@@ -1303,7 +1303,7 @@
         <v>45971</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>13</v>
@@ -1314,7 +1314,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C21" s="9">
         <v>2025</v>
@@ -1329,7 +1329,7 @@
         <v>45975</v>
       </c>
       <c r="G21" s="9">
-        <v>4918</v>
+        <v>4836</v>
       </c>
       <c r="H21" s="3">
         <v>45962</v>
@@ -1338,7 +1338,7 @@
         <v>45971</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>13</v>
@@ -1349,7 +1349,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C22" s="9">
         <v>2025</v>
@@ -1364,7 +1364,7 @@
         <v>45975</v>
       </c>
       <c r="G22" s="9">
-        <v>4905</v>
+        <v>4831</v>
       </c>
       <c r="H22" s="3">
         <v>45962</v>
@@ -1373,7 +1373,7 @@
         <v>45971</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>13</v>
@@ -1384,7 +1384,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C23" s="9">
         <v>2025</v>
@@ -1399,7 +1399,7 @@
         <v>45975</v>
       </c>
       <c r="G23" s="9">
-        <v>4896</v>
+        <v>4814</v>
       </c>
       <c r="H23" s="3">
         <v>45962</v>
@@ -1408,7 +1408,7 @@
         <v>45971</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>13</v>
@@ -1419,7 +1419,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C24" s="9">
         <v>2025</v>
@@ -1434,16 +1434,16 @@
         <v>45975</v>
       </c>
       <c r="G24" s="9">
-        <v>4863</v>
+        <v>4718</v>
       </c>
       <c r="H24" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I24" s="2">
         <v>45971</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>13</v>
@@ -1454,7 +1454,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C25" s="9">
         <v>2025</v>
@@ -1469,16 +1469,16 @@
         <v>45975</v>
       </c>
       <c r="G25" s="9">
-        <v>4845</v>
+        <v>4605</v>
       </c>
       <c r="H25" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I25" s="2">
         <v>45971</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K25" s="9" t="s">
         <v>13</v>
@@ -1489,7 +1489,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C26" s="9">
         <v>2025</v>
@@ -1504,16 +1504,16 @@
         <v>45975</v>
       </c>
       <c r="G26" s="9">
-        <v>4837</v>
+        <v>4326</v>
       </c>
       <c r="H26" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I26" s="2">
         <v>45971</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>13</v>
@@ -1539,7 +1539,7 @@
         <v>45975</v>
       </c>
       <c r="G27" s="9">
-        <v>4836</v>
+        <v>4736</v>
       </c>
       <c r="H27" s="3">
         <v>45962</v>
@@ -1548,7 +1548,7 @@
         <v>45971</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>13</v>
@@ -1574,16 +1574,16 @@
         <v>45975</v>
       </c>
       <c r="G28" s="9">
-        <v>4831</v>
+        <v>4319</v>
       </c>
       <c r="H28" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I28" s="2">
         <v>45971</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>13</v>
@@ -1594,7 +1594,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C29" s="9">
         <v>2025</v>
@@ -1609,7 +1609,7 @@
         <v>45975</v>
       </c>
       <c r="G29" s="9">
-        <v>4814</v>
+        <v>5274</v>
       </c>
       <c r="H29" s="3">
         <v>45962</v>
@@ -1618,7 +1618,7 @@
         <v>45971</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>13</v>
@@ -1629,7 +1629,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C30" s="9">
         <v>2025</v>
@@ -1644,7 +1644,7 @@
         <v>45975</v>
       </c>
       <c r="G30" s="9">
-        <v>4736</v>
+        <v>4918</v>
       </c>
       <c r="H30" s="3">
         <v>45962</v>
@@ -1653,7 +1653,7 @@
         <v>45971</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>13</v>
@@ -1664,7 +1664,7 @@
         <v>11</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C31" s="9">
         <v>2025</v>
@@ -1679,7 +1679,7 @@
         <v>45975</v>
       </c>
       <c r="G31" s="9">
-        <v>4718</v>
+        <v>4445</v>
       </c>
       <c r="H31" s="3">
         <v>45931</v>
@@ -1688,7 +1688,7 @@
         <v>45971</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>13</v>
@@ -1699,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="9">
         <v>2025</v>
@@ -1714,7 +1714,7 @@
         <v>45975</v>
       </c>
       <c r="G32" s="9">
-        <v>4677</v>
+        <v>4365</v>
       </c>
       <c r="H32" s="3">
         <v>45931</v>
@@ -1723,7 +1723,7 @@
         <v>45971</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>13</v>
@@ -1734,7 +1734,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C33" s="9">
         <v>2025</v>
@@ -1749,7 +1749,7 @@
         <v>45975</v>
       </c>
       <c r="G33" s="9">
-        <v>4605</v>
+        <v>4361</v>
       </c>
       <c r="H33" s="3">
         <v>45931</v>
@@ -1758,7 +1758,7 @@
         <v>45971</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>13</v>
@@ -1769,7 +1769,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C34" s="9">
         <v>2025</v>
@@ -1784,16 +1784,16 @@
         <v>45975</v>
       </c>
       <c r="G34" s="9">
-        <v>4595</v>
+        <v>4845</v>
       </c>
       <c r="H34" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I34" s="2">
         <v>45971</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>13</v>
@@ -1804,7 +1804,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C35" s="9">
         <v>2025</v>
@@ -1819,16 +1819,16 @@
         <v>45975</v>
       </c>
       <c r="G35" s="9">
-        <v>4578</v>
+        <v>5164</v>
       </c>
       <c r="H35" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I35" s="2">
         <v>45971</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>13</v>
@@ -1839,7 +1839,7 @@
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C36" s="9">
         <v>2025</v>
@@ -1854,16 +1854,16 @@
         <v>45975</v>
       </c>
       <c r="G36" s="9">
-        <v>4527</v>
+        <v>5273</v>
       </c>
       <c r="H36" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I36" s="2">
         <v>45971</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>13</v>
@@ -1874,7 +1874,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C37" s="9">
         <v>2025</v>
@@ -1889,16 +1889,16 @@
         <v>45975</v>
       </c>
       <c r="G37" s="9">
-        <v>4445</v>
+        <v>5188</v>
       </c>
       <c r="H37" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I37" s="2">
         <v>45971</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>13</v>
@@ -1909,7 +1909,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C38" s="9">
         <v>2025</v>
@@ -1924,16 +1924,16 @@
         <v>45975</v>
       </c>
       <c r="G38" s="9">
-        <v>4365</v>
+        <v>5026</v>
       </c>
       <c r="H38" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I38" s="2">
         <v>45971</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>13</v>
@@ -1944,7 +1944,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C39" s="9">
         <v>2025</v>
@@ -1959,7 +1959,7 @@
         <v>45975</v>
       </c>
       <c r="G39" s="9">
-        <v>4361</v>
+        <v>4595</v>
       </c>
       <c r="H39" s="3">
         <v>45931</v>
@@ -1968,7 +1968,7 @@
         <v>45971</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>13</v>
@@ -1979,7 +1979,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C40" s="9">
         <v>2025</v>
@@ -1994,7 +1994,7 @@
         <v>45975</v>
       </c>
       <c r="G40" s="9">
-        <v>4326</v>
+        <v>4578</v>
       </c>
       <c r="H40" s="3">
         <v>45931</v>
@@ -2003,7 +2003,7 @@
         <v>45971</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>13</v>
@@ -2014,7 +2014,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C41" s="9">
         <v>2025</v>
@@ -2029,7 +2029,7 @@
         <v>45975</v>
       </c>
       <c r="G41" s="9">
-        <v>4319</v>
+        <v>4305</v>
       </c>
       <c r="H41" s="3">
         <v>45931</v>
@@ -2064,7 +2064,7 @@
         <v>45975</v>
       </c>
       <c r="G42" s="9">
-        <v>4305</v>
+        <v>3974</v>
       </c>
       <c r="H42" s="3">
         <v>45931</v>
@@ -2084,7 +2084,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C43" s="9">
         <v>2025</v>
@@ -2099,10 +2099,10 @@
         <v>45975</v>
       </c>
       <c r="G43" s="9">
-        <v>4134</v>
+        <v>5185</v>
       </c>
       <c r="H43" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I43" s="2">
         <v>45971</v>
@@ -2119,7 +2119,7 @@
         <v>11</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C44" s="9">
         <v>2025</v>
@@ -2134,10 +2134,10 @@
         <v>45975</v>
       </c>
       <c r="G44" s="9">
-        <v>3974</v>
+        <v>5205</v>
       </c>
       <c r="H44" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I44" s="2">
         <v>45971</v>
@@ -2154,7 +2154,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C45" s="9">
         <v>2025</v>
@@ -2169,7 +2169,7 @@
         <v>45975</v>
       </c>
       <c r="G45" s="9">
-        <v>3264</v>
+        <v>4527</v>
       </c>
       <c r="H45" s="3">
         <v>45931</v>
@@ -2178,7 +2178,7 @@
         <v>45971</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>13</v>
@@ -2186,7 +2186,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K26" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K45">
       <sortCondition ref="B1:B26"/>
     </sortState>
   </autoFilter>
@@ -2254,7 +2254,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -2278,7 +2278,7 @@
         <v>45971</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
@@ -2289,7 +2289,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -2313,7 +2313,7 @@
         <v>45971</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>17</v>
@@ -2324,7 +2324,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -2348,7 +2348,7 @@
         <v>45971</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>17</v>
@@ -2359,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -2383,7 +2383,7 @@
         <v>45971</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>17</v>
@@ -2394,7 +2394,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
@@ -2418,7 +2418,7 @@
         <v>45971</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>17</v>
@@ -2429,7 +2429,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1">
         <v>2025</v>
@@ -2453,7 +2453,7 @@
         <v>45971</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>17</v>
@@ -2464,7 +2464,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
         <v>2025</v>
@@ -2499,7 +2499,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1">
         <v>2025</v>
@@ -2523,7 +2523,7 @@
         <v>45971</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>17</v>
@@ -2534,7 +2534,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
@@ -2569,7 +2569,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1">
         <v>2025</v>
@@ -2604,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1">
         <v>2025</v>
@@ -2639,7 +2639,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1">
         <v>2025</v>
@@ -2674,7 +2674,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
         <v>2025</v>
@@ -2709,7 +2709,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1">
         <v>2025</v>
